--- a/import/Корректировки/1 неделя/01.09.xlsx
+++ b/import/Корректировки/1 неделя/01.09.xlsx
@@ -1351,7 +1351,9 @@
       <c r="E7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="17"/>
+      <c r="F7" s="17">
+        <v>5</v>
+      </c>
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1366,7 +1368,9 @@
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2">
+        <v>6</v>
+      </c>
       <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1381,7 +1385,9 @@
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>7</v>
+      </c>
       <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1396,7 +1402,9 @@
       <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
       <c r="G10" s="22"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1411,7 +1419,9 @@
       <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1426,7 +1436,9 @@
       <c r="E12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3">
+        <v>6</v>
+      </c>
       <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1441,7 +1453,9 @@
       <c r="E13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3">
+        <v>7</v>
+      </c>
       <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1460,7 +1474,9 @@
       <c r="E14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1475,7 +1491,9 @@
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3">
+        <v>5</v>
+      </c>
       <c r="G15" s="22"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1490,7 +1508,9 @@
       <c r="E16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3">
+        <v>6</v>
+      </c>
       <c r="G16" s="22"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1505,7 +1525,9 @@
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3">
+        <v>7</v>
+      </c>
       <c r="G17" s="22"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1520,7 +1542,9 @@
       <c r="E18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
       <c r="G18" s="22"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1535,7 +1559,9 @@
       <c r="E19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3">
+        <v>5</v>
+      </c>
       <c r="G19" s="22"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1550,7 +1576,9 @@
       <c r="E20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3">
+        <v>6</v>
+      </c>
       <c r="G20" s="22"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1565,7 +1593,9 @@
       <c r="E21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3">
+        <v>7</v>
+      </c>
       <c r="G21" s="22"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1601,7 +1631,9 @@
       <c r="E23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
       <c r="G23" s="22"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1616,7 +1648,9 @@
       <c r="E24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3">
+        <v>4</v>
+      </c>
       <c r="G24" s="22"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1631,7 +1665,9 @@
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3">
+        <v>5</v>
+      </c>
       <c r="G25" s="22"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1646,7 +1682,9 @@
       <c r="E26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3">
+        <v>6</v>
+      </c>
       <c r="G26" s="22"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1661,7 +1699,9 @@
       <c r="E27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3">
+        <v>5</v>
+      </c>
       <c r="G27" s="22"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1676,7 +1716,9 @@
       <c r="E28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3">
+        <v>6</v>
+      </c>
       <c r="G28" s="22"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1695,7 +1737,9 @@
       <c r="E29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3">
+        <v>7</v>
+      </c>
       <c r="G29" s="22"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1710,7 +1754,9 @@
       <c r="E30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
       <c r="G30" s="22"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1725,7 +1771,9 @@
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3">
+        <v>4</v>
+      </c>
       <c r="G31" s="22"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1740,7 +1788,9 @@
       <c r="E32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3">
+        <v>5</v>
+      </c>
       <c r="G32" s="22"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1755,7 +1805,9 @@
       <c r="E33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3">
+        <v>6</v>
+      </c>
       <c r="G33" s="22"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1770,7 +1822,9 @@
       <c r="E34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3">
+        <v>7</v>
+      </c>
       <c r="G34" s="22"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1785,7 +1839,9 @@
       <c r="E35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3">
+        <v>5</v>
+      </c>
       <c r="G35" s="22"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1800,7 +1856,9 @@
       <c r="E36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3">
+        <v>6</v>
+      </c>
       <c r="G36" s="22"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1815,7 +1873,9 @@
       <c r="E37" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3">
+        <v>7</v>
+      </c>
       <c r="G37" s="22"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1830,7 +1890,9 @@
       <c r="E38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3">
+        <v>4</v>
+      </c>
       <c r="G38" s="22"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1845,7 +1907,9 @@
       <c r="E39" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3">
+        <v>6</v>
+      </c>
       <c r="G39" s="22"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1860,7 +1924,9 @@
       <c r="E40" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3">
+        <v>7</v>
+      </c>
       <c r="G40" s="22"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1875,7 +1941,9 @@
       <c r="E41" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
       <c r="G41" s="22"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1890,7 +1958,9 @@
       <c r="E42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3">
+        <v>5</v>
+      </c>
       <c r="G42" s="22"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1905,7 +1975,9 @@
       <c r="E43" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>6</v>
+      </c>
       <c r="G43" s="22"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1920,7 +1992,9 @@
       <c r="E44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3">
+        <v>7</v>
+      </c>
       <c r="G44" s="22"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1935,7 +2009,9 @@
       <c r="E45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3">
+        <v>5</v>
+      </c>
       <c r="G45" s="22"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1954,7 +2030,9 @@
       <c r="E46" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3">
+        <v>6</v>
+      </c>
       <c r="G46" s="22"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1969,7 +2047,9 @@
       <c r="E47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3">
+        <v>7</v>
+      </c>
       <c r="G47" s="22"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1984,7 +2064,9 @@
       <c r="E48" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F48" s="3"/>
+      <c r="F48" s="3">
+        <v>1</v>
+      </c>
       <c r="G48" s="22"/>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1999,7 +2081,9 @@
       <c r="E49" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3">
+        <v>5</v>
+      </c>
       <c r="G49" s="22"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2014,7 +2098,9 @@
       <c r="E50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3">
+        <v>6</v>
+      </c>
       <c r="G50" s="22"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2029,7 +2115,9 @@
       <c r="E51" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3">
+        <v>7</v>
+      </c>
       <c r="G51" s="22"/>
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2044,7 +2132,9 @@
       <c r="E52" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3">
+        <v>1</v>
+      </c>
       <c r="G52" s="22"/>
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2059,7 +2149,9 @@
       <c r="E53" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3">
+        <v>6</v>
+      </c>
       <c r="G53" s="22"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2074,7 +2166,9 @@
       <c r="E54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3">
+        <v>7</v>
+      </c>
       <c r="G54" s="22"/>
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2089,7 +2183,9 @@
       <c r="E55" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3">
+        <v>1</v>
+      </c>
       <c r="G55" s="22"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2104,7 +2200,9 @@
       <c r="E56" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
       <c r="G56" s="22"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2119,7 +2217,9 @@
       <c r="E57" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
       <c r="G57" s="22"/>
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2134,7 +2234,9 @@
       <c r="E58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F58" s="3"/>
+      <c r="F58" s="3">
+        <v>5</v>
+      </c>
       <c r="G58" s="22"/>
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2149,7 +2251,9 @@
       <c r="E59" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3">
+        <v>6</v>
+      </c>
       <c r="G59" s="22"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2164,7 +2268,9 @@
       <c r="E60" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3">
+        <v>7</v>
+      </c>
       <c r="G60" s="22"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2179,7 +2285,9 @@
       <c r="E61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3">
+        <v>5</v>
+      </c>
       <c r="G61" s="22"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2194,7 +2302,9 @@
       <c r="E62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F62" s="3"/>
+      <c r="F62" s="3">
+        <v>6</v>
+      </c>
       <c r="G62" s="22"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2209,7 +2319,9 @@
       <c r="E63" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3">
+        <v>7</v>
+      </c>
       <c r="G63" s="22"/>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2224,7 +2336,9 @@
       <c r="E64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3">
+        <v>5</v>
+      </c>
       <c r="G64" s="22"/>
     </row>
     <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2239,7 +2353,9 @@
       <c r="E65" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3">
+        <v>6</v>
+      </c>
       <c r="G65" s="22"/>
     </row>
     <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2254,7 +2370,9 @@
       <c r="E66" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3">
+        <v>7</v>
+      </c>
       <c r="G66" s="22"/>
     </row>
     <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2269,7 +2387,9 @@
       <c r="E67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3">
+        <v>1</v>
+      </c>
       <c r="G67" s="22"/>
     </row>
     <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2284,7 +2404,9 @@
       <c r="E68" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3">
+        <v>4</v>
+      </c>
       <c r="G68" s="22"/>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2299,7 +2421,9 @@
       <c r="E69" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
       <c r="G69" s="22"/>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2314,7 +2438,9 @@
       <c r="E70" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3">
+        <v>6</v>
+      </c>
       <c r="G70" s="22"/>
     </row>
     <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2329,7 +2455,9 @@
       <c r="E71" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3">
+        <v>7</v>
+      </c>
       <c r="G71" s="22"/>
     </row>
     <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2344,7 +2472,9 @@
       <c r="E72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3">
+        <v>1</v>
+      </c>
       <c r="G72" s="22"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2359,7 +2489,9 @@
       <c r="E73" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3">
+        <v>5</v>
+      </c>
       <c r="G73" s="22"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2374,7 +2506,9 @@
       <c r="E74" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3">
+        <v>6</v>
+      </c>
       <c r="G74" s="22"/>
     </row>
     <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2389,7 +2523,9 @@
       <c r="E75" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F75" s="3"/>
+      <c r="F75" s="3">
+        <v>7</v>
+      </c>
       <c r="G75" s="22"/>
     </row>
     <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2404,7 +2540,9 @@
       <c r="E76" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
       <c r="G76" s="22"/>
     </row>
     <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2419,7 +2557,9 @@
       <c r="E77" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3">
+        <v>5</v>
+      </c>
       <c r="G77" s="22"/>
     </row>
     <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2434,7 +2574,9 @@
       <c r="E78" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3">
+        <v>6</v>
+      </c>
       <c r="G78" s="22"/>
     </row>
     <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2449,7 +2591,9 @@
       <c r="E79" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F79" s="3"/>
+      <c r="F79" s="3">
+        <v>7</v>
+      </c>
       <c r="G79" s="22"/>
     </row>
     <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2464,7 +2608,9 @@
       <c r="E80" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3">
+        <v>1</v>
+      </c>
       <c r="G80" s="22"/>
     </row>
     <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2479,7 +2625,9 @@
       <c r="E81" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3">
+        <v>5</v>
+      </c>
       <c r="G81" s="22"/>
     </row>
     <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2494,7 +2642,9 @@
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3">
+        <v>6</v>
+      </c>
       <c r="G82" s="22"/>
     </row>
     <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2509,7 +2659,9 @@
       <c r="E83" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3">
+        <v>7</v>
+      </c>
       <c r="G83" s="22"/>
     </row>
     <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2524,7 +2676,9 @@
       <c r="E84" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3">
+        <v>5</v>
+      </c>
       <c r="G84" s="22"/>
     </row>
     <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2539,7 +2693,9 @@
       <c r="E85" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3">
+        <v>6</v>
+      </c>
       <c r="G85" s="22"/>
     </row>
     <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2554,7 +2710,9 @@
       <c r="E86" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3">
+        <v>7</v>
+      </c>
       <c r="G86" s="22"/>
     </row>
     <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2569,7 +2727,9 @@
       <c r="E87" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3">
+        <v>1</v>
+      </c>
       <c r="G87" s="22"/>
     </row>
     <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2584,7 +2744,9 @@
       <c r="E88" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3">
+        <v>5</v>
+      </c>
       <c r="G88" s="22"/>
     </row>
     <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2599,7 +2761,9 @@
       <c r="E89" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3">
+        <v>6</v>
+      </c>
       <c r="G89" s="22"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2614,7 +2778,9 @@
       <c r="E90" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3">
+        <v>7</v>
+      </c>
       <c r="G90" s="22"/>
     </row>
     <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2629,7 +2795,9 @@
       <c r="E91" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F91" s="3"/>
+      <c r="F91" s="3">
+        <v>5</v>
+      </c>
       <c r="G91" s="22"/>
     </row>
     <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2644,7 +2812,9 @@
       <c r="E92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3">
+        <v>6</v>
+      </c>
       <c r="G92" s="22"/>
     </row>
     <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2659,7 +2829,9 @@
       <c r="E93" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3">
+        <v>7</v>
+      </c>
       <c r="G93" s="22"/>
     </row>
     <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2674,7 +2846,9 @@
       <c r="E94" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3">
+        <v>1</v>
+      </c>
       <c r="G94" s="22"/>
     </row>
     <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2689,7 +2863,9 @@
       <c r="E95" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F95" s="3"/>
+      <c r="F95" s="3">
+        <v>4</v>
+      </c>
       <c r="G95" s="22"/>
     </row>
     <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2704,7 +2880,9 @@
       <c r="E96" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F96" s="3"/>
+      <c r="F96" s="3">
+        <v>5</v>
+      </c>
       <c r="G96" s="22"/>
     </row>
     <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2719,7 +2897,9 @@
       <c r="E97" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F97" s="3"/>
+      <c r="F97" s="3">
+        <v>6</v>
+      </c>
       <c r="G97" s="22"/>
     </row>
     <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2734,7 +2914,9 @@
       <c r="E98" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3">
+        <v>7</v>
+      </c>
       <c r="G98" s="22"/>
     </row>
     <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2749,7 +2931,9 @@
       <c r="E99" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3">
+        <v>4</v>
+      </c>
       <c r="G99" s="22"/>
     </row>
     <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2764,7 +2948,9 @@
       <c r="E100" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F100" s="3"/>
+      <c r="F100" s="3">
+        <v>5</v>
+      </c>
       <c r="G100" s="22"/>
     </row>
     <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2779,7 +2965,9 @@
       <c r="E101" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F101" s="3"/>
+      <c r="F101" s="3">
+        <v>6</v>
+      </c>
       <c r="G101" s="22"/>
     </row>
     <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2794,7 +2982,9 @@
       <c r="E102" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F102" s="3"/>
+      <c r="F102" s="3">
+        <v>5</v>
+      </c>
       <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2809,7 +2999,9 @@
       <c r="E103" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F103" s="3"/>
+      <c r="F103" s="3">
+        <v>6</v>
+      </c>
       <c r="G103" s="22"/>
     </row>
     <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2824,7 +3016,9 @@
       <c r="E104" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F104" s="3"/>
+      <c r="F104" s="3">
+        <v>7</v>
+      </c>
       <c r="G104" s="22"/>
     </row>
     <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2839,7 +3033,9 @@
       <c r="E105" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F105" s="3"/>
+      <c r="F105" s="3">
+        <v>1</v>
+      </c>
       <c r="G105" s="22"/>
     </row>
     <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2854,7 +3050,9 @@
       <c r="E106" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F106" s="3"/>
+      <c r="F106" s="3">
+        <v>6</v>
+      </c>
       <c r="G106" s="22"/>
     </row>
     <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2869,7 +3067,9 @@
       <c r="E107" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F107" s="3"/>
+      <c r="F107" s="3">
+        <v>7</v>
+      </c>
       <c r="G107" s="22"/>
     </row>
     <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2884,7 +3084,9 @@
       <c r="E108" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F108" s="3"/>
+      <c r="F108" s="3">
+        <v>6</v>
+      </c>
       <c r="G108" s="22"/>
     </row>
     <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2899,7 +3101,9 @@
       <c r="E109" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F109" s="3"/>
+      <c r="F109" s="3">
+        <v>7</v>
+      </c>
       <c r="G109" s="22"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2914,7 +3118,9 @@
       <c r="E110" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F110" s="3"/>
+      <c r="F110" s="3">
+        <v>1</v>
+      </c>
       <c r="G110" s="22"/>
     </row>
     <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2929,7 +3135,9 @@
       <c r="E111" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F111" s="3"/>
+      <c r="F111" s="3">
+        <v>4</v>
+      </c>
       <c r="G111" s="22"/>
     </row>
     <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2944,7 +3152,9 @@
       <c r="E112" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F112" s="3"/>
+      <c r="F112" s="3">
+        <v>5</v>
+      </c>
       <c r="G112" s="22"/>
     </row>
     <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2959,7 +3169,9 @@
       <c r="E113" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F113" s="3"/>
+      <c r="F113" s="3">
+        <v>4</v>
+      </c>
       <c r="G113" s="22"/>
     </row>
     <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2974,7 +3186,9 @@
       <c r="E114" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F114" s="3"/>
+      <c r="F114" s="3">
+        <v>5</v>
+      </c>
       <c r="G114" s="22"/>
     </row>
     <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2989,7 +3203,9 @@
       <c r="E115" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F115" s="3"/>
+      <c r="F115" s="3">
+        <v>6</v>
+      </c>
       <c r="G115" s="22"/>
     </row>
     <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3004,7 +3220,9 @@
       <c r="E116" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F116" s="3"/>
+      <c r="F116" s="3">
+        <v>7</v>
+      </c>
       <c r="G116" s="22"/>
     </row>
     <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3019,7 +3237,9 @@
       <c r="E117" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F117" s="3"/>
+      <c r="F117" s="3">
+        <v>5</v>
+      </c>
       <c r="G117" s="22"/>
     </row>
     <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3034,7 +3254,9 @@
       <c r="E118" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F118" s="3"/>
+      <c r="F118" s="3">
+        <v>6</v>
+      </c>
       <c r="G118" s="22"/>
     </row>
     <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3049,7 +3271,9 @@
       <c r="E119" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F119" s="3"/>
+      <c r="F119" s="3">
+        <v>7</v>
+      </c>
       <c r="G119" s="22"/>
     </row>
     <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3064,7 +3288,9 @@
       <c r="E120" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F120" s="3"/>
+      <c r="F120" s="3">
+        <v>1</v>
+      </c>
       <c r="G120" s="22"/>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3079,7 +3305,9 @@
       <c r="E121" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F121" s="3"/>
+      <c r="F121" s="3">
+        <v>6</v>
+      </c>
       <c r="G121" s="22"/>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3094,7 +3322,9 @@
       <c r="E122" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F122" s="3"/>
+      <c r="F122" s="3">
+        <v>7</v>
+      </c>
       <c r="G122" s="22"/>
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3109,7 +3339,9 @@
       <c r="E123" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F123" s="3"/>
+      <c r="F123" s="3">
+        <v>1</v>
+      </c>
       <c r="G123" s="22"/>
     </row>
     <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3124,7 +3356,9 @@
       <c r="E124" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F124" s="3"/>
+      <c r="F124" s="3">
+        <v>1</v>
+      </c>
       <c r="G124" s="22"/>
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3139,7 +3373,9 @@
       <c r="E125" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F125" s="3"/>
+      <c r="F125" s="3">
+        <v>6</v>
+      </c>
       <c r="G125" s="22"/>
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3154,7 +3390,9 @@
       <c r="E126" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3">
+        <v>7</v>
+      </c>
       <c r="G126" s="22"/>
     </row>
     <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3169,7 +3407,9 @@
       <c r="E127" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F127" s="3"/>
+      <c r="F127" s="3">
+        <v>1</v>
+      </c>
       <c r="G127" s="22"/>
     </row>
     <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3184,7 +3424,9 @@
       <c r="E128" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F128" s="3"/>
+      <c r="F128" s="3">
+        <v>1</v>
+      </c>
       <c r="G128" s="22"/>
     </row>
     <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3199,7 +3441,9 @@
       <c r="E129" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F129" s="3"/>
+      <c r="F129" s="3">
+        <v>5</v>
+      </c>
       <c r="G129" s="22"/>
     </row>
     <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3214,7 +3458,9 @@
       <c r="E130" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F130" s="3"/>
+      <c r="F130" s="3">
+        <v>6</v>
+      </c>
       <c r="G130" s="22"/>
     </row>
     <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3229,7 +3475,9 @@
       <c r="E131" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F131" s="3"/>
+      <c r="F131" s="3">
+        <v>7</v>
+      </c>
       <c r="G131" s="22"/>
     </row>
     <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3244,7 +3492,9 @@
       <c r="E132" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F132" s="3"/>
+      <c r="F132" s="3">
+        <v>6</v>
+      </c>
       <c r="G132" s="22"/>
     </row>
     <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3259,7 +3509,9 @@
       <c r="E133" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F133" s="3"/>
+      <c r="F133" s="3">
+        <v>7</v>
+      </c>
       <c r="G133" s="22"/>
     </row>
     <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3274,7 +3526,9 @@
       <c r="E134" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F134" s="3"/>
+      <c r="F134" s="3">
+        <v>1</v>
+      </c>
       <c r="G134" s="22"/>
     </row>
     <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3289,7 +3543,9 @@
       <c r="E135" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F135" s="3"/>
+      <c r="F135" s="3">
+        <v>1</v>
+      </c>
       <c r="G135" s="22"/>
     </row>
     <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3304,7 +3560,9 @@
       <c r="E136" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F136" s="3"/>
+      <c r="F136" s="3">
+        <v>1</v>
+      </c>
       <c r="G136" s="22"/>
     </row>
     <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3319,7 +3577,9 @@
       <c r="E137" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F137" s="3"/>
+      <c r="F137" s="3">
+        <v>2</v>
+      </c>
       <c r="G137" s="22"/>
     </row>
     <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3334,7 +3594,9 @@
       <c r="E138" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F138" s="3"/>
+      <c r="F138" s="3">
+        <v>1</v>
+      </c>
       <c r="G138" s="22"/>
     </row>
     <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3349,7 +3611,9 @@
       <c r="E139" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F139" s="3"/>
+      <c r="F139" s="3">
+        <v>6</v>
+      </c>
       <c r="G139" s="22"/>
     </row>
     <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3364,7 +3628,9 @@
       <c r="E140" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F140" s="3"/>
+      <c r="F140" s="3">
+        <v>7</v>
+      </c>
       <c r="G140" s="22"/>
     </row>
     <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3400,7 +3666,9 @@
       <c r="E142" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F142" s="3"/>
+      <c r="F142" s="3">
+        <v>5</v>
+      </c>
       <c r="G142" s="22"/>
     </row>
     <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3415,7 +3683,9 @@
       <c r="E143" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F143" s="3"/>
+      <c r="F143" s="3">
+        <v>6</v>
+      </c>
       <c r="G143" s="22"/>
     </row>
     <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3430,7 +3700,9 @@
       <c r="E144" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F144" s="3"/>
+      <c r="F144" s="3">
+        <v>7</v>
+      </c>
       <c r="G144" s="22"/>
     </row>
     <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3445,7 +3717,9 @@
       <c r="E145" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F145" s="3"/>
+      <c r="F145" s="3">
+        <v>6</v>
+      </c>
       <c r="G145" s="22"/>
     </row>
     <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3460,7 +3734,9 @@
       <c r="E146" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F146" s="3"/>
+      <c r="F146" s="3">
+        <v>7</v>
+      </c>
       <c r="G146" s="22"/>
     </row>
     <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3475,7 +3751,9 @@
       <c r="E147" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F147" s="3"/>
+      <c r="F147" s="3">
+        <v>1</v>
+      </c>
       <c r="G147" s="22"/>
     </row>
     <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3511,7 +3789,9 @@
       <c r="E149" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F149" s="3"/>
+      <c r="F149" s="3">
+        <v>5</v>
+      </c>
       <c r="G149" s="22"/>
     </row>
     <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3526,7 +3806,9 @@
       <c r="E150" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F150" s="3"/>
+      <c r="F150" s="3">
+        <v>6</v>
+      </c>
       <c r="G150" s="22"/>
     </row>
     <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3541,7 +3823,9 @@
       <c r="E151" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F151" s="3"/>
+      <c r="F151" s="3">
+        <v>1</v>
+      </c>
       <c r="G151" s="22"/>
     </row>
     <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3556,7 +3840,9 @@
       <c r="E152" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F152" s="3"/>
+      <c r="F152" s="3">
+        <v>7</v>
+      </c>
       <c r="G152" s="22"/>
     </row>
     <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3571,7 +3857,9 @@
       <c r="E153" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F153" s="3"/>
+      <c r="F153" s="3">
+        <v>2</v>
+      </c>
       <c r="G153" s="22"/>
     </row>
     <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3586,7 +3874,9 @@
       <c r="E154" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F154" s="3"/>
+      <c r="F154" s="3">
+        <v>4</v>
+      </c>
       <c r="G154" s="22"/>
     </row>
     <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3601,7 +3891,9 @@
       <c r="E155" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F155" s="3"/>
+      <c r="F155" s="3">
+        <v>5</v>
+      </c>
       <c r="G155" s="22"/>
     </row>
     <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3616,7 +3908,9 @@
       <c r="E156" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F156" s="3"/>
+      <c r="F156" s="3">
+        <v>6</v>
+      </c>
       <c r="G156" s="22"/>
     </row>
     <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3631,7 +3925,9 @@
       <c r="E157" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F157" s="3"/>
+      <c r="F157" s="3">
+        <v>1</v>
+      </c>
       <c r="G157" s="22"/>
     </row>
     <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3646,7 +3942,9 @@
       <c r="E158" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F158" s="3"/>
+      <c r="F158" s="3">
+        <v>5</v>
+      </c>
       <c r="G158" s="22"/>
     </row>
     <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3661,7 +3959,9 @@
       <c r="E159" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F159" s="3"/>
+      <c r="F159" s="3">
+        <v>6</v>
+      </c>
       <c r="G159" s="22"/>
     </row>
     <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3676,7 +3976,9 @@
       <c r="E160" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F160" s="3"/>
+      <c r="F160" s="3">
+        <v>7</v>
+      </c>
       <c r="G160" s="22"/>
     </row>
     <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3691,7 +3993,9 @@
       <c r="E161" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F161" s="3"/>
+      <c r="F161" s="3">
+        <v>5</v>
+      </c>
       <c r="G161" s="22"/>
     </row>
     <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3706,7 +4010,9 @@
       <c r="E162" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F162" s="3"/>
+      <c r="F162" s="3">
+        <v>6</v>
+      </c>
       <c r="G162" s="22"/>
     </row>
     <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3721,7 +4027,9 @@
       <c r="E163" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F163" s="3"/>
+      <c r="F163" s="3">
+        <v>7</v>
+      </c>
       <c r="G163" s="22"/>
     </row>
     <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3736,7 +4044,9 @@
       <c r="E164" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F164" s="3"/>
+      <c r="F164" s="3">
+        <v>1</v>
+      </c>
       <c r="G164" s="22"/>
     </row>
     <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3751,7 +4061,9 @@
       <c r="E165" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F165" s="3"/>
+      <c r="F165" s="3">
+        <v>5</v>
+      </c>
       <c r="G165" s="22"/>
     </row>
     <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3766,7 +4078,9 @@
       <c r="E166" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F166" s="3"/>
+      <c r="F166" s="3">
+        <v>6</v>
+      </c>
       <c r="G166" s="22"/>
     </row>
     <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3781,7 +4095,9 @@
       <c r="E167" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F167" s="3"/>
+      <c r="F167" s="3">
+        <v>7</v>
+      </c>
       <c r="G167" s="22"/>
     </row>
     <row r="168" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3796,7 +4112,9 @@
       <c r="E168" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F168" s="3"/>
+      <c r="F168" s="3">
+        <v>4</v>
+      </c>
       <c r="G168" s="22"/>
     </row>
     <row r="169" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3811,7 +4129,9 @@
       <c r="E169" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F169" s="3"/>
+      <c r="F169" s="3">
+        <v>5</v>
+      </c>
       <c r="G169" s="22"/>
     </row>
     <row r="170" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3826,7 +4146,9 @@
       <c r="E170" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F170" s="3"/>
+      <c r="F170" s="3">
+        <v>6</v>
+      </c>
       <c r="G170" s="22"/>
     </row>
     <row r="171" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3841,7 +4163,9 @@
       <c r="E171" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F171" s="3"/>
+      <c r="F171" s="3">
+        <v>5</v>
+      </c>
       <c r="G171" s="22"/>
     </row>
     <row r="172" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3856,7 +4180,9 @@
       <c r="E172" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F172" s="3"/>
+      <c r="F172" s="3">
+        <v>6</v>
+      </c>
       <c r="G172" s="22"/>
     </row>
     <row r="173" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3871,7 +4197,9 @@
       <c r="E173" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F173" s="3"/>
+      <c r="F173" s="3">
+        <v>7</v>
+      </c>
       <c r="G173" s="22"/>
     </row>
     <row r="174" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3886,7 +4214,9 @@
       <c r="E174" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F174" s="3"/>
+      <c r="F174" s="3">
+        <v>1</v>
+      </c>
       <c r="G174" s="22"/>
     </row>
     <row r="175" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3901,7 +4231,9 @@
       <c r="E175" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F175" s="3"/>
+      <c r="F175" s="3">
+        <v>5</v>
+      </c>
       <c r="G175" s="22"/>
     </row>
     <row r="176" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3937,7 +4269,9 @@
       <c r="E177" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F177" s="3"/>
+      <c r="F177" s="3">
+        <v>6</v>
+      </c>
       <c r="G177" s="22"/>
     </row>
     <row r="178" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3952,7 +4286,9 @@
       <c r="E178" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F178" s="3"/>
+      <c r="F178" s="3">
+        <v>7</v>
+      </c>
       <c r="G178" s="22"/>
     </row>
     <row r="179" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3967,7 +4303,9 @@
       <c r="E179" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F179" s="3"/>
+      <c r="F179" s="3">
+        <v>1</v>
+      </c>
       <c r="G179" s="22"/>
     </row>
     <row r="180" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3986,7 +4324,9 @@
       <c r="E180" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F180" s="3"/>
+      <c r="F180" s="3">
+        <v>1</v>
+      </c>
       <c r="G180" s="22"/>
     </row>
     <row r="181" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4001,7 +4341,9 @@
       <c r="E181" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F181" s="3"/>
+      <c r="F181" s="3">
+        <v>5</v>
+      </c>
       <c r="G181" s="22"/>
     </row>
     <row r="182" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4016,7 +4358,9 @@
       <c r="E182" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F182" s="3"/>
+      <c r="F182" s="3">
+        <v>6</v>
+      </c>
       <c r="G182" s="22"/>
     </row>
     <row r="183" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4031,7 +4375,9 @@
       <c r="E183" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F183" s="3"/>
+      <c r="F183" s="3">
+        <v>7</v>
+      </c>
       <c r="G183" s="22"/>
     </row>
     <row r="184" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4046,7 +4392,9 @@
       <c r="E184" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F184" s="3"/>
+      <c r="F184" s="3">
+        <v>1</v>
+      </c>
       <c r="G184" s="22"/>
     </row>
     <row r="185" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">

--- a/import/Корректировки/1 неделя/01.09.xlsx
+++ b/import/Корректировки/1 неделя/01.09.xlsx
@@ -1462,12 +1462,8 @@
       <c r="A14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1725,12 +1721,8 @@
       <c r="A29" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
         <v>33</v>
       </c>
@@ -2018,12 +2010,8 @@
       <c r="A46" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
         <v>13</v>
       </c>
